--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>730736-101-CM25</t>
+          <t>2564-86-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.090.700-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE CHEPICA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>17300.27</v>
+        <v>39601.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2564-86-CM25</t>
+          <t>730736-101-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>39601.69</v>
+        <v>17300.27</v>
       </c>
     </row>
     <row r="9">
@@ -1502,7 +1502,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4139-189-CM25</t>
+          <t>4139-190-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1557,13 +1557,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>17341.55</v>
+        <v>25738.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4139-190-CM25</t>
+          <t>4139-189-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1603,12 +1603,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>25738.03</v>
+        <v>17341.55</v>
       </c>
     </row>
     <row r="20">
@@ -1685,7 +1685,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3996-411-CM25</t>
+          <t>3996-412-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MEDITERRANEO AUTOMOTORES S A</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.889.440-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1740,13 +1740,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>68610.06</v>
+        <v>35252.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3996-412-CM25</t>
+          <t>3996-411-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>35252.15</v>
+        <v>68610.06</v>
       </c>
     </row>
     <row r="23">
@@ -2173,7 +2173,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2777-901-CM25</t>
+          <t>2675-465-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2193,17 +2193,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2228,13 +2228,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>24833.15</v>
+        <v>31112.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2675-465-CM25</t>
+          <t>2777-901-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2254,17 +2254,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2274,12 +2274,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>31112.96</v>
+        <v>24833.15</v>
       </c>
     </row>
     <row r="31">
@@ -2478,7 +2478,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>557639-28-CM26</t>
+          <t>557639-29-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2533,13 +2533,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>70974.39999999999</v>
+        <v>21587.92</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>557639-29-CM26</t>
+          <t>557639-28-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2579,12 +2579,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2594,7 +2594,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>21587.92</v>
+        <v>70974.39999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2905,7 +2905,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2565-243-CM26</t>
+          <t>2675-179-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>22148.18</v>
+        <v>64961.98</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2675-179-CM26</t>
+          <t>3764-296-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.090.400-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE NANCAGUA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>64961.98</v>
+        <v>21001.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3764-296-CM26</t>
+          <t>730736-155-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.090.400-4</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>21001.1</v>
+        <v>27148.63</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>730736-155-CM26</t>
+          <t>3889-247-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3103,22 +3103,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.090.200-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE PLACILLA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>27148.63</v>
+        <v>14384.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3889-247-CM26</t>
+          <t>3764-336-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,22 +3164,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.090.200-1</t>
+          <t>69.090.400-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PLACILLA</t>
+          <t>I MUNICIPALIDAD DE NANCAGUA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3204,13 +3204,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>14384.16</v>
+        <v>38998.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3764-336-CM26</t>
+          <t>4139-194-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3220,27 +3220,27 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.090.400-4</t>
+          <t>69.091.000-4</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NANCAGUA</t>
+          <t>I MUNICIPALIDAD DE PALMILLA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>38998.09</v>
+        <v>40092.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4139-194-CM26</t>
+          <t>3014-167-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.091.000-4</t>
+          <t>69.081.600-8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PALMILLA</t>
+          <t>I MUNICIPALIDAD DE COINCO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SKC Transportes S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.176.602-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>40092.11</v>
+        <v>22671.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3014-167-CM26</t>
+          <t>3864-154-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.081.600-8</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COINCO</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SKC Transportes S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.176.602-3</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3387,13 +3387,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>22671.8</v>
+        <v>37771.44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3864-154-CM26</t>
+          <t>1743-374-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>37771.44</v>
+        <v>40718.63</v>
       </c>
     </row>
     <row r="50">
@@ -3515,7 +3515,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1743-374-CM26</t>
+          <t>1743-373-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>40718.63</v>
+        <v>587.8099999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3637,7 +3637,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1743-373-CM26</t>
+          <t>804962-126-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,12 +3677,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>587.8099999999999</v>
+        <v>23825.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1284047-46-CM26</t>
+          <t>804962-127-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>65.057.349-8</t>
+          <t>69.081.400-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE OLIVAR</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>28640.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>804962-126-CM26</t>
+          <t>3963-29-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>69.080.900-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>I MUNICIPALIDAD DE PEUMO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3814,13 +3814,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>23825.17</v>
+        <v>48853.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>804962-127-CM26</t>
+          <t>4374-44-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.081.400-5</t>
+          <t>72.240.400-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLIVAR</t>
+          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3875,13 +3875,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0</v>
+        <v>25010.09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3963-29-CM26</t>
+          <t>2675-373-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.080.900-1</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEUMO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Inchcape Camiones y Buses Chile S.A.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>48853.59</v>
+        <v>12972.86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>4374-44-CM26</t>
+          <t>2776-548-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>72.240.400-9</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VI REGION DEL LI BERTADOR B O"HIGGINS</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>25010.09</v>
+        <v>38916.73</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2776-548-CM26</t>
+          <t>1501728-57-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>38916.73</v>
+        <v>47565.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2675-373-CM26</t>
+          <t>1223542-174-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>77.050.575-5</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>12972.86</v>
+        <v>13638.66</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1501728-57-CM26</t>
+          <t>1223542-175-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>77.050.575-5</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4180,7 +4180,434 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>47565.79</v>
+        <v>197.3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>642-179-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.818.000-K</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>61013.48</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4371-408-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.081.000-k</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>PORTILLO S.A.</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>77.008.670-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>34485.94</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4371-409-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>69.081.000-k</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>PORTILLO S.A.</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>77.008.670-1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>217.61</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1284047-51-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>65.057.349-8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>27534.66</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1284047-52-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>65.057.349-8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>1582.54</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>3181-417-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>69.080.200-7</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>30208.85</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3181-418-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.080.200-7</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>445.69</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -810,7 +814,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +879,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +944,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1009,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1074,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1139,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1265,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1395,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1550,7 +1586,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1611,7 +1651,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1672,7 +1716,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1733,7 +1781,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1794,7 +1846,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1855,7 +1911,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1916,7 +1976,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1977,7 +2041,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2038,7 +2106,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2160,7 +2232,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2221,7 +2297,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2526,7 +2606,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2587,7 +2671,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2648,7 +2736,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2709,7 +2801,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2770,7 +2866,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2892,7 +2992,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3014,7 +3118,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3075,7 +3183,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3136,7 +3248,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3197,7 +3313,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3258,7 +3378,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3380,7 +3504,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3563,7 +3691,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3624,7 +3756,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3685,7 +3821,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3746,7 +3886,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3807,7 +3951,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3868,7 +4016,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3929,7 +4081,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3990,7 +4146,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4051,7 +4211,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4112,7 +4276,11 @@
           <t>77.050.575-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4173,7 +4341,11 @@
           <t>77.050.575-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4234,7 +4406,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4417,7 +4593,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4478,7 +4658,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4539,7 +4723,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4600,7 +4788,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3057,7 +3057,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3521,7 +3525,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1743-374-CM26</t>
+          <t>1743-375-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3576,13 +3580,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>40718.63</v>
+        <v>1101.28</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1743-375-CM26</t>
+          <t>1743-374-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3637,13 +3641,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1101.28</v>
+        <v>40718.63</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1743-373-CM26</t>
+          <t>1743-372-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3702,13 +3706,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>587.8099999999999</v>
+        <v>29376.24</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1743-372-CM26</t>
+          <t>1743-373-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3767,7 +3771,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>29376.24</v>
+        <v>587.8099999999999</v>
       </c>
     </row>
     <row r="53">
@@ -4033,7 +4037,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2675-373-CM26</t>
+          <t>2675-370-SE26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4048,7 +4052,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4073,17 +4077,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4092,7 +4096,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>12972.86</v>
+        <v>66453.3</v>
       </c>
     </row>
     <row r="58">
@@ -4163,7 +4167,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1501728-57-CM26</t>
+          <t>2675-373-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4178,7 +4182,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4188,12 +4192,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4203,17 +4207,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4222,13 +4226,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>47565.79</v>
+        <v>12972.86</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1223542-174-CM26</t>
+          <t>1501728-57-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4238,12 +4242,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4253,12 +4257,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>65.104.928-8</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4268,17 +4272,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>FK SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.050.575-5</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4287,13 +4291,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>13638.66</v>
+        <v>47565.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1223542-175-CM26</t>
+          <t>1223542-174-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4352,13 +4356,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>197.3</v>
+        <v>13638.66</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>642-179-CM26</t>
+          <t>1223542-175-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4373,7 +4377,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4383,12 +4387,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.818.000-K</t>
+          <t>65.104.928-8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE RANCAGUA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4398,12 +4402,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>FK SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>77.050.575-5</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -4417,13 +4421,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>61013.48</v>
+        <v>197.3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>4371-408-CM26</t>
+          <t>642-179-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4438,7 +4442,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4448,12 +4452,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>61.818.000-K</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VI REGION</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4463,28 +4467,32 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>PORTILLO S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.008.670-1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>34485.94</v>
+        <v>61013.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4371-409-CM26</t>
+          <t>4371-408-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4539,13 +4547,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>217.61</v>
+        <v>34485.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1284047-51-CM26</t>
+          <t>4371-409-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4560,7 +4568,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4570,12 +4578,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>65.057.349-8</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4585,32 +4593,28 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>PORTILLO S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>77.008.670-1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>27534.66</v>
+        <v>217.61</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1284047-52-CM26</t>
+          <t>1284047-51-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4669,13 +4673,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1582.54</v>
+        <v>27534.66</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3181-417-CM26</t>
+          <t>1284047-52-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4690,7 +4694,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4700,12 +4704,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>65.057.349-8</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>CORPORACION CULTURAL DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4715,17 +4719,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.928.530-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4734,71 +4738,136 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>30208.85</v>
+        <v>1582.54</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>3181-417-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.080.200-7</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>30208.85</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
           <t>3181-418-CM26</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>69.080.200-7</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
         <is>
           <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="n">
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
         <v>445.69</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2564-86-CM25</t>
+          <t>730736-101-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -856,12 +856,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.090.700-3</t>
+          <t>69.090.900-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHEPICA</t>
+          <t>I MUNICIPALIDAD DE PAREDONES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>39601.69</v>
+        <v>17300.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>730736-101-CM25</t>
+          <t>2564-86-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.090.900-6</t>
+          <t>69.090.700-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAREDONES</t>
+          <t>I MUNICIPALIDAD DE CHEPICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>17300.27</v>
+        <v>39601.69</v>
       </c>
     </row>
     <row r="9">
@@ -2249,7 +2249,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2675-465-CM25</t>
+          <t>2777-901-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2269,17 +2269,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2289,32 +2289,28 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>86.385.500-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>31112.96</v>
+        <v>24833.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2777-901-CM25</t>
+          <t>2675-465-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2334,17 +2330,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2354,22 +2350,26 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>24833.15</v>
+        <v>31112.96</v>
       </c>
     </row>
     <row r="31">
@@ -3525,7 +3525,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1743-375-CM26</t>
+          <t>1743-373-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3565,28 +3565,32 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1101.28</v>
+        <v>587.8099999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1743-374-CM26</t>
+          <t>1743-375-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3641,13 +3645,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>40718.63</v>
+        <v>1101.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1743-372-CM26</t>
+          <t>1743-374-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3687,32 +3691,28 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>29376.24</v>
+        <v>40718.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1743-373-CM26</t>
+          <t>1743-372-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>587.8099999999999</v>
+        <v>29376.24</v>
       </c>
     </row>
     <row r="53">
@@ -4102,7 +4102,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2776-548-CM26</t>
+          <t>2675-373-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4122,17 +4122,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.081.200-2</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENGO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -4161,13 +4161,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>38916.73</v>
+        <v>12972.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2675-373-CM26</t>
+          <t>2776-548-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4187,17 +4187,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.081.200-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE RENGO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -4226,7 +4226,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>12972.86</v>
+        <v>38916.73</v>
       </c>
     </row>
     <row r="60">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4492,7 +4492,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4371-408-CM26</t>
+          <t>4371-409-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>34485.94</v>
+        <v>217.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4371-409-CM26</t>
+          <t>4371-408-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>217.61</v>
+        <v>34485.94</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1284047-51-CM26</t>
+          <t>1284047-52-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4673,13 +4673,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>27534.66</v>
+        <v>1582.54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1284047-52-CM26</t>
+          <t>1284047-51-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4738,13 +4738,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1582.54</v>
+        <v>27534.66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3181-417-CM26</t>
+          <t>3181-418-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4803,13 +4803,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>30208.85</v>
+        <v>445.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3181-418-CM26</t>
+          <t>3181-417-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4829,46 +4829,111 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>69.080.200-7</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>30208.85</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1079563-449-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>69.080.200-7</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>COMERCIAL AUTOMOTRIZ SPA</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>96.928.530-4</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>445.69</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.978.680-7</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>34940.12</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/o-higgins.xlsx
@@ -3545,7 +3545,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
